--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>131287281</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>8442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58264</v>
+        <v>58270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -816,7 +816,7 @@
         <v>131287281</v>
       </c>
       <c r="B3" t="n">
-        <v>8442</v>
+        <v>8443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58270</v>
+        <v>58271</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58058</v>
+        <v>58061</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58271</v>
+        <v>58274</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131286638</v>
       </c>
       <c r="B2" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
         <v>131287054</v>
       </c>
       <c r="B4" t="n">
-        <v>58274</v>
+        <v>58276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131286638</v>
+        <v>131287054</v>
       </c>
       <c r="B2" t="n">
-        <v>58063</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -716,7 +716,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>558643</v>
+        <v>558647</v>
       </c>
       <c r="R2" t="n">
-        <v>6584842</v>
+        <v>6584845</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,12 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sjungande talltita i barrblandskog med flertalet lämpliga boplatser som murkna björkhögstubbar.</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -813,41 +808,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131287281</v>
+        <v>131286638</v>
       </c>
       <c r="B3" t="n">
-        <v>8443</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -857,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>558632</v>
+        <v>558643</v>
       </c>
       <c r="R3" t="n">
-        <v>6584841</v>
+        <v>6584842</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -902,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sjungande talltita i barrblandskog med flertalet lämpliga boplatser som murkna björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +918,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -922,7 +928,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrblandskog med död ved. Stående och liggande</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131287054</v>
+        <v>131287281</v>
       </c>
       <c r="B4" t="n">
-        <v>58276</v>
+        <v>8444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,37 +957,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -991,10 +990,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>558647</v>
+        <v>558632</v>
       </c>
       <c r="R4" t="n">
-        <v>6584845</v>
+        <v>6584841</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1045,6 +1044,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Barrblandskog med död ved. Stående och liggande</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 2850-2026 artfynd.xlsx
+++ b/artfynd/A 2850-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -805,6 +810,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131287054</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -943,6 +953,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131286638</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1070,8 +1085,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131287281</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>